--- a/data-manipulation-scripts/sheets-cleanup/sheets/BORRACHA PEDALEIRA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BORRACHA PEDALEIRA.xlsx
@@ -31,7 +31,7 @@
     <t>070341174913</t>
   </si>
   <si>
-    <t>BORRACHA PEDALEIRA TRASEIRA VHSV TITAN FAN160 181178</t>
+    <t>BORRACHA PEDALEIRA TRASEIRA PAR VHSV TITAN FAN160 181178</t>
   </si>
   <si>
     <t>8714.10.00</t>
@@ -40,19 +40,19 @@
     <t>7897570131868</t>
   </si>
   <si>
-    <t>BORRACHA PEDALEIRA ESTRIBO MOTOBOR+ BIZ100 44277</t>
+    <t>BORRACHA PEDALEIRA ESTRIBO PAR MOTOBOR+ BIZ100 44277</t>
   </si>
   <si>
     <t>7893986286055</t>
   </si>
   <si>
-    <t>BORRACHA PEDALEIRA ESTRIBO PEÇA+ BROS NXR150</t>
+    <t>BORRACHA PEDALEIRA ESTRIBO PAR PEÇA+ BROS NXR150</t>
   </si>
   <si>
     <t>7898456460812</t>
   </si>
   <si>
-    <t>BORRACHA PEDALEIRA ESTRIBO VEDOX BIZ</t>
+    <t>BORRACHA PEDALEIRA ESTRIBO PAR VEDOX BIZ</t>
   </si>
   <si>
     <t>7908285455702</t>
@@ -64,7 +64,7 @@
     <t>7893986177186</t>
   </si>
   <si>
-    <t>BORRACHA ESTRIBO PEÇA+ YBR</t>
+    <t>BORRACHA ESTRIBO PAR PEÇA+ YBR</t>
   </si>
   <si>
     <t>7898751863301</t>
@@ -128,10 +128,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -404,10 +404,12 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>4.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>15.0</v>
+      </c>
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
@@ -440,10 +442,12 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>10.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E3" s="6" t="s">
         <v>7</v>
       </c>
@@ -476,10 +480,12 @@
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>4.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E4" s="6" t="s">
         <v>7</v>
       </c>
@@ -509,13 +515,15 @@
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="8">
         <v>2.0</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="4">
+        <v>18.0</v>
+      </c>
       <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
@@ -551,7 +559,9 @@
       <c r="C6" s="8">
         <v>4.0</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E6" s="6" t="s">
         <v>7</v>
       </c>
@@ -581,7 +591,7 @@
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="8">
